--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_ABS-CSTD-0-01-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_ABS-CSTD-0-01-A-C0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\shamoto\Sprint62\設計書\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2BD4C6-7514-4054-BFF1-C4C37DEE41A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="22680" windowHeight="10470" tabRatio="620"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" tabRatio="620" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -22,17 +23,30 @@
     <sheet name="Reference" sheetId="25" r:id="rId8"/>
     <sheet name="History" sheetId="7" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="B10" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -49,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -66,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -86,12 +100,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -137,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -153,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -187,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -208,13 +222,13 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -229,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="1" shapeId="0">
+    <comment ref="F2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -257,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -272,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -293,7 +307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -308,7 +322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="1" shapeId="0">
+    <comment ref="J2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -324,7 +338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
       <text>
         <r>
           <rPr>
@@ -340,7 +354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="1" shapeId="0">
+    <comment ref="L2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -355,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="1" shapeId="0">
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
       <text>
         <r>
           <rPr>
@@ -375,13 +389,13 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
       <text>
         <r>
           <rPr>
@@ -398,7 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="1" shapeId="0">
+    <comment ref="C9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
       <text>
         <r>
           <rPr>
@@ -414,7 +428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="1" shapeId="0">
+    <comment ref="E9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
       <text>
         <r>
           <rPr>
@@ -430,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="1" shapeId="0">
+    <comment ref="F9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
       <text>
         <r>
           <rPr>
@@ -445,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="1" shapeId="0">
+    <comment ref="G9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
       <text>
         <r>
           <rPr>
@@ -461,7 +475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="1" shapeId="0">
+    <comment ref="H9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000006000000}">
       <text>
         <r>
           <rPr>
@@ -477,7 +491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="1" shapeId="0">
+    <comment ref="I9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000007000000}">
       <text>
         <r>
           <rPr>
@@ -493,7 +507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="J9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000008000000}">
       <text>
         <r>
           <rPr>
@@ -508,7 +522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B78" authorId="0" shapeId="0">
+    <comment ref="B78" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000009000000}">
       <text>
         <r>
           <rPr>
@@ -525,7 +539,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C81" authorId="1" shapeId="0">
+    <comment ref="C81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -541,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E81" authorId="1" shapeId="0">
+    <comment ref="E81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -557,7 +571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F81" authorId="1" shapeId="0">
+    <comment ref="F81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -572,7 +586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G81" authorId="1" shapeId="0">
+    <comment ref="G81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -588,7 +602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H81" authorId="1" shapeId="0">
+    <comment ref="H81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -604,7 +618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I81" authorId="1" shapeId="0">
+    <comment ref="I81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -620,7 +634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J81" authorId="1" shapeId="0">
+    <comment ref="J81" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000010000000}">
       <text>
         <r>
           <rPr>
@@ -640,7 +654,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4665" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4665" uniqueCount="337">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2723,13 +2737,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95</t>
-  </si>
-  <si>
     <t>RWT_EN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2921,27 +2928,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>DDRTWV</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>B_ABS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3166,11 +3157,19 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>DDM1S17_STS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DDM1S17</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21">
     <font>
       <sz val="11"/>
@@ -5220,37 +5219,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5295,10 +5273,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5359,9 +5358,9 @@
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="標準 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -5439,16 +5438,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -5493,7 +5482,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6282,7 +6277,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7071,7 +7072,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="線吹き出し 1 (枠付き) 55"/>
+        <xdr:cNvPr id="56" name="線吹き出し 1 (枠付き) 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7209,7 +7216,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="線吹き出し 1 (枠付き) 59"/>
+        <xdr:cNvPr id="60" name="線吹き出し 1 (枠付き) 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7347,7 +7360,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7385,7 +7404,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7423,7 +7448,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7461,7 +7492,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7499,7 +7536,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5"/>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7537,7 +7580,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7575,7 +7624,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7"/>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7613,7 +7668,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8"/>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7651,7 +7712,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="正方形/長方形 56"/>
+        <xdr:cNvPr id="57" name="正方形/長方形 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7711,7 +7778,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="73" name="正方形/長方形 72"/>
+        <xdr:cNvPr id="73" name="正方形/長方形 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7771,7 +7844,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="85" name="正方形/長方形 84"/>
+        <xdr:cNvPr id="85" name="正方形/長方形 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7831,7 +7910,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="86" name="正方形/長方形 85"/>
+        <xdr:cNvPr id="86" name="正方形/長方形 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7891,7 +7976,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="87" name="正方形/長方形 86"/>
+        <xdr:cNvPr id="87" name="正方形/長方形 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7951,7 +8042,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="88" name="正方形/長方形 87"/>
+        <xdr:cNvPr id="88" name="正方形/長方形 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8011,7 +8108,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="90" name="正方形/長方形 89"/>
+        <xdr:cNvPr id="90" name="正方形/長方形 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8071,7 +8174,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="91" name="線吹き出し 1 (枠付き) 90"/>
+        <xdr:cNvPr id="91" name="線吹き出し 1 (枠付き) 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8146,7 +8255,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="92" name="線吹き出し 1 (枠付き) 91"/>
+        <xdr:cNvPr id="92" name="線吹き出し 1 (枠付き) 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8229,7 +8344,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="93" name="正方形/長方形 92"/>
+        <xdr:cNvPr id="93" name="正方形/長方形 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8289,7 +8410,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="94" name="正方形/長方形 93"/>
+        <xdr:cNvPr id="94" name="正方形/長方形 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8349,7 +8476,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="95" name="正方形/長方形 94"/>
+        <xdr:cNvPr id="95" name="正方形/長方形 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8409,7 +8542,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="96" name="正方形/長方形 95"/>
+        <xdr:cNvPr id="96" name="正方形/長方形 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8469,7 +8608,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="97" name="正方形/長方形 96"/>
+        <xdr:cNvPr id="97" name="正方形/長方形 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8529,7 +8674,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="109" name="線吹き出し 1 (枠付き) 108"/>
+        <xdr:cNvPr id="109" name="線吹き出し 1 (枠付き) 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8735,7 +8886,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="110" name="線吹き出し 1 (枠付き) 109"/>
+        <xdr:cNvPr id="110" name="線吹き出し 1 (枠付き) 109">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00006E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8963,7 +9120,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="111" name="正方形/長方形 110"/>
+        <xdr:cNvPr id="111" name="正方形/長方形 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00006F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9023,7 +9186,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="112" name="線吹き出し 1 (枠付き) 111"/>
+        <xdr:cNvPr id="112" name="線吹き出し 1 (枠付き) 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000070000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9117,7 +9286,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="113" name="正方形/長方形 112"/>
+        <xdr:cNvPr id="113" name="正方形/長方形 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9177,7 +9352,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="114" name="正方形/長方形 113"/>
+        <xdr:cNvPr id="114" name="正方形/長方形 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9237,7 +9418,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="115" name="線吹き出し 1 (枠付き) 114"/>
+        <xdr:cNvPr id="115" name="線吹き出し 1 (枠付き) 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9312,7 +9499,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="116" name="線吹き出し 1 (枠付き) 115"/>
+        <xdr:cNvPr id="116" name="線吹き出し 1 (枠付き) 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9395,7 +9588,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="117" name="正方形/長方形 116"/>
+        <xdr:cNvPr id="117" name="正方形/長方形 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9455,7 +9654,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="118" name="線吹き出し 1 (枠付き) 117"/>
+        <xdr:cNvPr id="118" name="線吹き出し 1 (枠付き) 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9604,7 +9809,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="119" name="正方形/長方形 118"/>
+        <xdr:cNvPr id="119" name="正方形/長方形 118">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9664,7 +9875,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="120" name="線吹き出し 1 (枠付き) 119"/>
+        <xdr:cNvPr id="120" name="線吹き出し 1 (枠付き) 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000078000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9750,7 +9967,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="121" name="正方形/長方形 120"/>
+        <xdr:cNvPr id="121" name="正方形/長方形 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9810,7 +10033,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="122" name="正方形/長方形 121"/>
+        <xdr:cNvPr id="122" name="正方形/長方形 121">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9870,7 +10099,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="123" name="線吹き出し 1 (枠付き) 122"/>
+        <xdr:cNvPr id="123" name="線吹き出し 1 (枠付き) 122">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9964,7 +10199,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="124" name="線吹き出し 1 (枠付き) 123"/>
+        <xdr:cNvPr id="124" name="線吹き出し 1 (枠付き) 123">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10096,7 +10337,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="126" name="線吹き出し 1 (枠付き) 125"/>
+        <xdr:cNvPr id="126" name="線吹き出し 1 (枠付き) 125">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10179,7 +10426,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="127" name="線吹き出し 1 (枠付き) 126"/>
+        <xdr:cNvPr id="127" name="線吹き出し 1 (枠付き) 126">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10265,7 +10518,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="図 127"/>
+        <xdr:cNvPr id="128" name="図 127">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000080000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -10309,7 +10568,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="129" name="正方形/長方形 128"/>
+        <xdr:cNvPr id="129" name="正方形/長方形 128">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000081000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10369,7 +10634,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="130" name="正方形/長方形 129"/>
+        <xdr:cNvPr id="130" name="正方形/長方形 129">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000082000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10429,7 +10700,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="131" name="線吹き出し 1 (枠付き) 130"/>
+        <xdr:cNvPr id="131" name="線吹き出し 1 (枠付き) 130">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000083000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10578,7 +10855,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="132" name="直線コネクタ 8"/>
+        <xdr:cNvPr id="132" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000084000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -10629,7 +10912,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="133" name="直線コネクタ 8"/>
+        <xdr:cNvPr id="133" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000085000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -10680,7 +10969,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="134" name="正方形/長方形 133"/>
+        <xdr:cNvPr id="134" name="正方形/長方形 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000086000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10754,7 +11049,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53"/>
+        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10886,7 +11187,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="線吹き出し 1 (枠付き) 54"/>
+        <xdr:cNvPr id="55" name="線吹き出し 1 (枠付き) 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11092,7 +11399,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="線吹き出し 1 (枠付き) 57"/>
+        <xdr:cNvPr id="58" name="線吹き出し 1 (枠付き) 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11305,13 +11618,565 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>238363</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>113505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>488074</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>34052</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{432CF261-2C68-4B26-BD7D-B6AD65682468}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20885006" y="12644508"/>
+          <a:ext cx="873992" cy="715085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>34052</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>102156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>414229</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>156904</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951EDB5C-E413-4EF8-B3D4-2A68A394D20D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14437895" y="11838620"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 86811"/>
+            <a:gd name="adj4" fmla="val 287714"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>DDM1S17</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>VSC1S95</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>374568</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>11351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>130465</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>66100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A375C3B9-3E92-4788-B515-352C647B15B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14154131" y="19171073"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 92647"/>
+            <a:gd name="adj4" fmla="val 303331"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>DDM1S17</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>VSC1S95</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>317815</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>11351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>295114</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>59157</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BDAD0DA-64CE-45D5-A297-919BC0A6CB40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20964458" y="19965612"/>
+          <a:ext cx="1850140" cy="842344"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -11349,9 +12214,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -11386,7 +12251,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -11421,7 +12286,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -11594,16 +12459,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -11673,7 +12538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:18" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:18">
       <c r="C7" s="238" t="s">
         <v>0</v>
@@ -11753,7 +12618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="13.5" thickTop="1">
+    <row r="9" spans="2:18" ht="13.6" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -11789,13 +12654,13 @@
         <v>31</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="N9" s="208">
         <v>43972</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="P9" s="208">
         <v>43972</v>
@@ -11807,55 +12672,55 @@
         <v>43909</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="91">
+    <row r="10" spans="2:18" ht="90.35">
       <c r="B10" s="10">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10" s="235" t="s">
+        <v>328</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="D10" s="235" t="s">
-        <v>334</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="N10" s="237">
         <v>44070</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="P10" s="237">
         <v>44070</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="R10" s="236">
         <v>44038</v>
@@ -11905,7 +12770,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" ht="13.5" thickBot="1">
+    <row r="13" spans="2:18" ht="13.6" thickBot="1">
       <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -11938,22 +12803,25 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11967,13 +12835,13 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="163" t="s">
         <v>142</v>
       </c>
       <c r="C6" s="163"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="85" t="s">
         <v>144</v>
       </c>
@@ -11993,7 +12861,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="25.85">
       <c r="C9" s="173">
         <v>1</v>
       </c>
@@ -12004,7 +12872,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="171"/>
       <c r="D10" s="96"/>
       <c r="E10" s="6"/>
@@ -12012,14 +12880,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="169"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="164" t="s">
         <v>143</v>
       </c>
       <c r="C12" s="92"/>
       <c r="D12" s="92"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="165"/>
       <c r="C13" s="170" t="s">
         <v>144</v>
@@ -12031,7 +12899,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="167">
         <v>0</v>
       </c>
@@ -12108,17 +12976,17 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="171"/>
       <c r="D21" s="96"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="163" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="170" t="s">
         <v>144</v>
       </c>
@@ -12140,7 +13008,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="168">
         <v>1</v>
       </c>
@@ -12205,12 +13073,12 @@
       <c r="D33" s="95"/>
       <c r="E33" s="81"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="171"/>
       <c r="D34" s="96"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="163" t="s">
         <v>177</v>
       </c>
@@ -12222,7 +13090,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
       <c r="C39" s="249"/>
       <c r="D39" s="250"/>
       <c r="E39" s="6" t="s">
@@ -12236,147 +13104,150 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1"/>
-    <hyperlink ref="E9" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="277"/>
-      <c r="D2" s="264" t="s">
-        <v>331</v>
-      </c>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266"/>
+      <c r="C2" s="252"/>
+      <c r="D2" s="257" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="251" t="s">
+      <c r="B3" s="253" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="252"/>
-      <c r="D3" s="267" t="s">
-        <v>332</v>
-      </c>
-      <c r="E3" s="268"/>
-      <c r="F3" s="268"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="260" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="262" t="s">
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="263"/>
-      <c r="D4" s="270" t="str">
+      <c r="C4" s="256"/>
+      <c r="D4" s="263" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_ABS-CSTD-0-01-A-C0.c</v>
       </c>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="272"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="265"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="276" t="s">
+      <c r="B6" s="251" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="277"/>
-      <c r="D6" s="273" t="str">
+      <c r="C6" s="252"/>
+      <c r="D6" s="266" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_ABS</v>
       </c>
-      <c r="E6" s="274"/>
-      <c r="F6" s="274"/>
-      <c r="G6" s="274"/>
-      <c r="H6" s="275"/>
+      <c r="E6" s="267"/>
+      <c r="F6" s="267"/>
+      <c r="G6" s="267"/>
+      <c r="H6" s="268"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="251" t="s">
+      <c r="B7" s="253" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="252"/>
-      <c r="D7" s="253">
+      <c r="C7" s="254"/>
+      <c r="D7" s="269">
         <f>COUNTA($D$13:$D$37)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="254"/>
-      <c r="F7" s="254"/>
-      <c r="G7" s="254"/>
-      <c r="H7" s="255"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="270"/>
+      <c r="G7" s="270"/>
+      <c r="H7" s="271"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="251" t="s">
+      <c r="B8" s="253" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="252"/>
-      <c r="D8" s="253" t="str">
+      <c r="C8" s="254"/>
+      <c r="D8" s="269" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_ABS_MTRX</v>
       </c>
-      <c r="E8" s="254"/>
-      <c r="F8" s="254"/>
-      <c r="G8" s="254"/>
-      <c r="H8" s="255"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="270"/>
+      <c r="G8" s="270"/>
+      <c r="H8" s="271"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="251" t="s">
+      <c r="B9" s="253" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="252"/>
-      <c r="D9" s="256" t="s">
-        <v>338</v>
-      </c>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="258"/>
+      <c r="C9" s="254"/>
+      <c r="D9" s="272" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="274"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="262" t="s">
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="255" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="263"/>
-      <c r="D10" s="259">
+      <c r="C10" s="256"/>
+      <c r="D10" s="275">
         <v>164</v>
       </c>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="261"/>
+      <c r="E10" s="276"/>
+      <c r="F10" s="276"/>
+      <c r="G10" s="276"/>
+      <c r="H10" s="277"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="154" t="s">
         <v>38</v>
       </c>
@@ -12411,7 +13282,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="114">
         <v>1</v>
       </c>
@@ -13270,7 +14141,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="105">
         <v>25</v>
       </c>
@@ -13311,32 +14182,27 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="9" priority="3">
-      <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
@@ -13344,46 +14210,54 @@
       <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="expression" dxfId="7" priority="3">
+      <formula>14 &lt; LEN($D$6)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"○,－"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$K$13:$K$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$L$13:$L$14</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" display="https://top.dndev.net/svn/met/"/>
+    <hyperlink ref="D3" r:id="rId1" display="https://top.dndev.net/svn/met/" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>204</v>
       </c>
@@ -13391,7 +14265,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="154" t="s">
         <v>38</v>
       </c>
@@ -13429,7 +14303,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="184">
         <v>0</v>
       </c>
@@ -13457,7 +14331,7 @@
       </c>
       <c r="R4" s="149"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="13.6" thickTop="1">
       <c r="B5" s="187">
         <v>1</v>
       </c>
@@ -13985,7 +14859,7 @@
       <c r="Q28" s="158"/>
       <c r="R28" s="126"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="188">
         <v>25</v>
       </c>
@@ -14007,7 +14881,7 @@
       <c r="Q29" s="156"/>
       <c r="R29" s="128"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>205</v>
       </c>
@@ -14015,7 +14889,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="154" t="s">
         <v>38</v>
       </c>
@@ -14047,7 +14921,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="184">
         <v>0</v>
       </c>
@@ -14073,7 +14947,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="187">
         <v>1</v>
       </c>
@@ -14601,7 +15475,7 @@
       <c r="Q58" s="158"/>
       <c r="R58" s="189"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="188">
         <v>25</v>
       </c>
@@ -14630,48 +15504,51 @@
   </protectedRanges>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"OPT,HW"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"DEF"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="98" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="106" t="s">
         <v>62</v>
       </c>
@@ -14715,7 +15592,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="26"/>
       <c r="C3" s="57" t="s">
         <v>114</v>
@@ -14736,12 +15613,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="26" t="s">
         <v>228</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D4" s="122">
         <v>0</v>
@@ -14750,7 +15627,7 @@
         <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G4" s="123" t="s">
         <v>137</v>
@@ -14791,7 +15668,7 @@
         <v>228</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D5" s="125">
         <v>1</v>
@@ -14841,7 +15718,7 @@
         <v>228</v>
       </c>
       <c r="C6" s="115" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D6" s="129">
         <v>2</v>
@@ -14891,7 +15768,7 @@
         <v>228</v>
       </c>
       <c r="C7" s="116" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D7" s="129">
         <v>3</v>
@@ -14962,7 +15839,7 @@
         <v>137</v>
       </c>
       <c r="J8" s="126" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="K8" s="26" t="s">
         <v>137</v>
@@ -15092,7 +15969,7 @@
       </c>
       <c r="U12" s="34"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="26"/>
       <c r="C13" s="25"/>
       <c r="D13" s="125"/>
@@ -17343,7 +18220,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="59"/>
       <c r="C103" s="60"/>
       <c r="D103" s="127"/>
@@ -17374,33 +18251,31 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
+  <conditionalFormatting sqref="M3:M103">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>Matrix!$H$13:$H$37</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B103</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
           <x14:formula1>
             <xm:f>Config_IF!$C$4:$C$29</xm:f>
           </x14:formula1>
@@ -17413,23 +18288,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17548,7 +18423,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="141" t="s">
         <v>139</v>
       </c>
@@ -17632,14 +18507,14 @@
         <v>66</v>
       </c>
       <c r="AD3" s="288" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="AE3" s="287"/>
       <c r="AF3" s="234" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG3" s="286" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AH3" s="286"/>
       <c r="AI3" s="287"/>
@@ -17648,7 +18523,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="282" t="s">
         <v>67</v>
       </c>
@@ -17696,7 +18571,7 @@
       <c r="AV4" s="88"/>
       <c r="AW4" s="89"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="284"/>
       <c r="B5" s="285"/>
       <c r="C5" s="204"/>
@@ -18126,7 +19001,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="25" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18389,7 +19264,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="25" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AL10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19184,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="25" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AL16" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19213,7 +20088,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="144"/>
       <c r="C17" s="53">
         <f t="shared" si="2"/>
@@ -19316,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL17" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19448,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="25" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AL18" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19814,7 +20689,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL21" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21888,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="AJ38" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL38" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22010,7 +22885,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL39" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22132,7 +23007,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22254,7 +23129,7 @@
         <v>1</v>
       </c>
       <c r="AJ41" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL41" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22376,7 +23251,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22498,7 +23373,7 @@
         <v>1</v>
       </c>
       <c r="AJ43" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL43" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22620,7 +23495,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL44" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22742,7 +23617,7 @@
         <v>1</v>
       </c>
       <c r="AJ45" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL45" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22864,7 +23739,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL46" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22986,7 +23861,7 @@
         <v>1</v>
       </c>
       <c r="AJ47" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL47" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23108,7 +23983,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL48" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23230,7 +24105,7 @@
         <v>1</v>
       </c>
       <c r="AJ49" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL49" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23352,7 +24227,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL50" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23474,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="AJ51" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL51" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23596,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL52" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23718,7 +24593,7 @@
         <v>1</v>
       </c>
       <c r="AJ53" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL53" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23840,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL54" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23962,7 +24837,7 @@
         <v>1</v>
       </c>
       <c r="AJ55" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL55" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24084,7 +24959,7 @@
         <v>0</v>
       </c>
       <c r="AJ56" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL56" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24206,7 +25081,7 @@
         <v>1</v>
       </c>
       <c r="AJ57" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL57" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24328,7 +25203,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL58" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24450,7 +25325,7 @@
         <v>1</v>
       </c>
       <c r="AJ59" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL59" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24572,7 +25447,7 @@
         <v>0</v>
       </c>
       <c r="AJ60" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL60" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24694,7 +25569,7 @@
         <v>1</v>
       </c>
       <c r="AJ61" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL61" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24816,7 +25691,7 @@
         <v>0</v>
       </c>
       <c r="AJ62" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL62" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -24938,7 +25813,7 @@
         <v>1</v>
       </c>
       <c r="AJ63" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL63" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25060,7 +25935,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL64" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25182,7 +26057,7 @@
         <v>1</v>
       </c>
       <c r="AJ65" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL65" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25304,7 +26179,7 @@
         <v>0</v>
       </c>
       <c r="AJ66" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL66" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25426,7 +26301,7 @@
         <v>1</v>
       </c>
       <c r="AJ67" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL67" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25548,7 +26423,7 @@
         <v>0</v>
       </c>
       <c r="AJ68" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL68" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25670,7 +26545,7 @@
         <v>1</v>
       </c>
       <c r="AJ69" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL69" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25689,7 +26564,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_C_ABS_TT_ON_RW                                               /* 63 ON_RW                                           */</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="62" t="s">
         <v>68</v>
       </c>
@@ -46295,16 +47170,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Search Table, Index Table"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
           </x14:formula1>
@@ -46317,23 +47195,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -46452,7 +47330,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="141" t="s">
         <v>139</v>
       </c>
@@ -46545,18 +47423,18 @@
         <v>66</v>
       </c>
       <c r="AG3" s="288" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="AH3" s="287"/>
       <c r="AI3" s="233" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AJ3" s="281"/>
       <c r="AR3" s="99" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="282" t="s">
         <v>67</v>
       </c>
@@ -46604,7 +47482,7 @@
       <c r="AV4" s="88"/>
       <c r="AW4" s="89"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="284"/>
       <c r="B5" s="285"/>
       <c r="C5" s="204"/>
@@ -48115,7 +48993,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="144"/>
       <c r="C17" s="53">
         <f t="shared" si="2"/>
@@ -54485,7 +55363,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="62" t="s">
         <v>68</v>
       </c>
@@ -75088,16 +75966,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Search Table, Index Table"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0600-000001000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
           </x14:formula1>
@@ -75110,25 +75991,25 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:R87"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="34.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="12" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="12" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="10.90625" customWidth="1"/>
+    <col min="15" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.5" thickBot="1">
+    <row r="2" spans="2:18" ht="15.65" thickBot="1">
       <c r="B2" s="27" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.5" thickBot="1">
+    <row r="3" spans="2:18" ht="15.65" thickBot="1">
       <c r="B3" s="103" t="s">
         <v>234</v>
       </c>
@@ -75211,7 +76092,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="26">
+    <row r="6" spans="2:18" ht="25.85">
       <c r="B6" s="77" t="s">
         <v>37</v>
       </c>
@@ -75258,7 +76139,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="26">
+    <row r="7" spans="2:18" ht="25.85">
       <c r="B7" s="78" t="s">
         <v>27</v>
       </c>
@@ -75273,58 +76154,58 @@
       <c r="I7" s="290"/>
       <c r="J7" s="291"/>
       <c r="K7" s="29" t="s">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="N7" s="35"/>
       <c r="O7" s="46"/>
       <c r="P7" s="84"/>
       <c r="Q7" s="84"/>
       <c r="R7" s="81" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="62">
+    <row r="8" spans="2:18" ht="61.15">
       <c r="B8" s="77" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="200" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D8" s="200" t="s">
         <v>66</v>
       </c>
       <c r="E8" s="200" t="s">
+        <v>245</v>
+      </c>
+      <c r="F8" s="200" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="200" t="s">
         <v>247</v>
       </c>
-      <c r="F8" s="200" t="s">
+      <c r="H8" s="200" t="s">
         <v>248</v>
-      </c>
-      <c r="G8" s="200" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" s="200" t="s">
-        <v>250</v>
       </c>
       <c r="I8" s="200" t="s">
         <v>173</v>
       </c>
       <c r="J8" s="200" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>295</v>
+        <v>335</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N8" s="34" t="s">
         <v>29</v>
@@ -75333,61 +76214,61 @@
       <c r="P8" s="84"/>
       <c r="Q8" s="84"/>
       <c r="R8" s="212" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="91.5" thickBot="1">
+    <row r="9" spans="2:18" ht="91.05" thickBot="1">
       <c r="B9" s="79" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D9" s="177" t="s">
         <v>239</v>
       </c>
       <c r="E9" s="177" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F9" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G9" s="177" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H9" s="177" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I9" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J9" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K9" s="30" t="s">
         <v>215</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O9" s="32" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P9" s="150"/>
       <c r="Q9" s="82"/>
       <c r="R9" s="213" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="13.5" thickTop="1">
+    <row r="10" spans="2:18" ht="13.6" thickTop="1">
       <c r="B10" s="80" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C10" s="178" t="s">
         <v>174</v>
@@ -75417,7 +76298,7 @@
         <v>32</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M10" s="41" t="s">
         <v>219</v>
@@ -75436,7 +76317,7 @@
     </row>
     <row r="11" spans="2:18">
       <c r="B11" s="23" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C11" s="179" t="s">
         <v>174</v>
@@ -75466,7 +76347,7 @@
         <v>32</v>
       </c>
       <c r="L11" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M11" s="38" t="s">
         <v>220</v>
@@ -75485,7 +76366,7 @@
     </row>
     <row r="12" spans="2:18">
       <c r="B12" s="23" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C12" s="179" t="s">
         <v>174</v>
@@ -75515,26 +76396,26 @@
         <v>32</v>
       </c>
       <c r="L12" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M12" s="38" t="s">
         <v>221</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="O12" s="45" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="P12" s="48"/>
       <c r="Q12" s="48"/>
       <c r="R12" s="201" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" s="23" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C13" s="179" t="s">
         <v>174</v>
@@ -75564,16 +76445,16 @@
         <v>32</v>
       </c>
       <c r="L13" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M13" s="38" t="s">
         <v>222</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="O13" s="45" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="P13" s="48"/>
       <c r="Q13" s="48"/>
@@ -75583,7 +76464,7 @@
     </row>
     <row r="14" spans="2:18">
       <c r="B14" s="23" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C14" s="179" t="s">
         <v>174</v>
@@ -75613,16 +76494,16 @@
         <v>32</v>
       </c>
       <c r="L14" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M14" s="38" t="s">
         <v>223</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="O14" s="45" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="P14" s="48"/>
       <c r="Q14" s="48"/>
@@ -75632,7 +76513,7 @@
     </row>
     <row r="15" spans="2:18">
       <c r="B15" s="23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C15" s="179" t="s">
         <v>174</v>
@@ -75662,7 +76543,7 @@
         <v>32</v>
       </c>
       <c r="L15" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M15" s="38" t="s">
         <v>224</v>
@@ -75681,7 +76562,7 @@
     </row>
     <row r="16" spans="2:18">
       <c r="B16" s="23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C16" s="179" t="s">
         <v>174</v>
@@ -75711,7 +76592,7 @@
         <v>32</v>
       </c>
       <c r="L16" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M16" s="38" t="s">
         <v>225</v>
@@ -75730,7 +76611,7 @@
     </row>
     <row r="17" spans="2:18">
       <c r="B17" s="23" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C17" s="179" t="s">
         <v>174</v>
@@ -75760,7 +76641,7 @@
         <v>32</v>
       </c>
       <c r="L17" s="207" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M17" s="216" t="s">
         <v>226</v>
@@ -75769,7 +76650,7 @@
         <v>213</v>
       </c>
       <c r="O17" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P17" s="48"/>
       <c r="Q17" s="48"/>
@@ -75779,7 +76660,7 @@
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="23" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C18" s="179" t="s">
         <v>174</v>
@@ -75809,7 +76690,7 @@
         <v>32</v>
       </c>
       <c r="L18" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M18" s="216" t="s">
         <v>219</v>
@@ -75828,7 +76709,7 @@
     </row>
     <row r="19" spans="2:18">
       <c r="B19" s="23" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C19" s="179" t="s">
         <v>174</v>
@@ -75858,7 +76739,7 @@
         <v>32</v>
       </c>
       <c r="L19" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M19" s="216" t="s">
         <v>220</v>
@@ -75877,7 +76758,7 @@
     </row>
     <row r="20" spans="2:18">
       <c r="B20" s="23" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C20" s="179" t="s">
         <v>174</v>
@@ -75907,16 +76788,16 @@
         <v>32</v>
       </c>
       <c r="L20" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M20" s="216" t="s">
         <v>221</v>
       </c>
       <c r="N20" s="44" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="O20" s="45" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P20" s="48"/>
       <c r="Q20" s="48"/>
@@ -75926,7 +76807,7 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" s="80" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C21" s="179" t="s">
         <v>174</v>
@@ -75956,26 +76837,26 @@
         <v>32</v>
       </c>
       <c r="L21" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M21" s="217" t="s">
         <v>222</v>
       </c>
       <c r="N21" s="42" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="O21" s="43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
       <c r="R21" s="201" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="2:18">
       <c r="B22" s="23" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C22" s="179" t="s">
         <v>174</v>
@@ -76005,16 +76886,16 @@
         <v>32</v>
       </c>
       <c r="L22" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M22" s="216" t="s">
         <v>223</v>
       </c>
       <c r="N22" s="44" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="O22" s="45" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P22" s="48"/>
       <c r="Q22" s="48"/>
@@ -76024,7 +76905,7 @@
     </row>
     <row r="23" spans="2:18">
       <c r="B23" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C23" s="179" t="s">
         <v>174</v>
@@ -76054,7 +76935,7 @@
         <v>32</v>
       </c>
       <c r="L23" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M23" s="216" t="s">
         <v>224</v>
@@ -76073,7 +76954,7 @@
     </row>
     <row r="24" spans="2:18">
       <c r="B24" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C24" s="179" t="s">
         <v>174</v>
@@ -76103,7 +76984,7 @@
         <v>32</v>
       </c>
       <c r="L24" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M24" s="216" t="s">
         <v>225</v>
@@ -76122,7 +77003,7 @@
     </row>
     <row r="25" spans="2:18">
       <c r="B25" s="23" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C25" s="179" t="s">
         <v>174</v>
@@ -76152,26 +77033,26 @@
         <v>32</v>
       </c>
       <c r="L25" s="67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M25" s="216" t="s">
         <v>226</v>
       </c>
       <c r="N25" s="44" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="O25" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P25" s="48"/>
       <c r="Q25" s="48"/>
       <c r="R25" s="201" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="2:18">
       <c r="B26" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C26" s="179" t="s">
         <v>174</v>
@@ -76201,7 +77082,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="67" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M26" s="216" t="s">
         <v>217</v>
@@ -76220,7 +77101,7 @@
     </row>
     <row r="27" spans="2:18">
       <c r="B27" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C27" s="179" t="s">
         <v>174</v>
@@ -76250,26 +77131,26 @@
         <v>35</v>
       </c>
       <c r="L27" s="67" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M27" s="216" t="s">
         <v>217</v>
       </c>
       <c r="N27" s="44" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="O27" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P27" s="48"/>
       <c r="Q27" s="48"/>
       <c r="R27" s="201" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="2:18">
       <c r="B28" s="23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C28" s="179" t="s">
         <v>174</v>
@@ -76299,26 +77180,26 @@
         <v>36</v>
       </c>
       <c r="L28" s="67" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M28" s="216" t="s">
         <v>217</v>
       </c>
       <c r="N28" s="44" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="O28" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P28" s="48"/>
       <c r="Q28" s="48"/>
       <c r="R28" s="201" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C29" s="219" t="s">
         <v>174</v>
@@ -76345,10 +77226,10 @@
         <v>174</v>
       </c>
       <c r="K29" s="221" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L29" s="221" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M29" s="222" t="s">
         <v>217</v>
@@ -76365,12 +77246,12 @@
         <v>239</v>
       </c>
     </row>
-    <row r="74" spans="2:18" ht="14.5" thickBot="1">
+    <row r="74" spans="2:18" ht="15.65" thickBot="1">
       <c r="B74" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="75" spans="2:18" ht="14.5" thickBot="1">
+    <row r="75" spans="2:18" ht="15.65" thickBot="1">
       <c r="B75" s="103" t="s">
         <v>234</v>
       </c>
@@ -76396,7 +77277,7 @@
     <row r="76" spans="2:18">
       <c r="B76" s="76"/>
       <c r="C76" s="37" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D76" s="37"/>
       <c r="E76" s="37"/>
@@ -76409,7 +77290,7 @@
       <c r="L76" s="37"/>
       <c r="M76" s="210"/>
       <c r="N76" s="33" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O76" s="49" t="s">
         <v>20</v>
@@ -76423,7 +77304,7 @@
         <v>21</v>
       </c>
       <c r="C77" s="295" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D77" s="290"/>
       <c r="E77" s="290"/>
@@ -76438,7 +77319,7 @@
       <c r="L77" s="202"/>
       <c r="M77" s="211"/>
       <c r="N77" s="34" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O77" s="83" t="s">
         <v>25</v>
@@ -76458,7 +77339,7 @@
         <v>37</v>
       </c>
       <c r="C78" s="176" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D78" s="176" t="s">
         <v>239</v>
@@ -76467,7 +77348,7 @@
         <v>239</v>
       </c>
       <c r="F78" s="176" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G78" s="176" t="s">
         <v>240</v>
@@ -76489,14 +77370,14 @@
       </c>
       <c r="M78" s="231"/>
       <c r="N78" s="34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O78" s="84"/>
       <c r="P78" s="46"/>
       <c r="Q78" s="84"/>
       <c r="R78" s="149"/>
     </row>
-    <row r="79" spans="2:18" ht="26">
+    <row r="79" spans="2:18" ht="25.85">
       <c r="B79" s="78" t="s">
         <v>27</v>
       </c>
@@ -76511,10 +77392,10 @@
       <c r="I79" s="290"/>
       <c r="J79" s="291"/>
       <c r="K79" s="1" t="s">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="L79" s="29" t="s">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="M79" s="149"/>
       <c r="N79" s="35"/>
@@ -76523,39 +77404,39 @@
       <c r="Q79" s="84"/>
       <c r="R79" s="149"/>
     </row>
-    <row r="80" spans="2:18" ht="62">
+    <row r="80" spans="2:18" ht="61.15">
       <c r="B80" s="77" t="s">
         <v>28</v>
       </c>
       <c r="C80" s="200" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D80" s="200" t="s">
         <v>66</v>
       </c>
       <c r="E80" s="200" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F80" s="200" t="s">
+        <v>246</v>
+      </c>
+      <c r="G80" s="200" t="s">
+        <v>271</v>
+      </c>
+      <c r="H80" s="200" t="s">
         <v>248</v>
       </c>
-      <c r="G80" s="200" t="s">
-        <v>273</v>
-      </c>
-      <c r="H80" s="200" t="s">
-        <v>250</v>
-      </c>
       <c r="I80" s="200" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J80" s="200" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="L80" s="29" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M80" s="149"/>
       <c r="N80" s="34" t="s">
@@ -76566,54 +77447,54 @@
       <c r="Q80" s="84"/>
       <c r="R80" s="149"/>
     </row>
-    <row r="81" spans="2:18" ht="65.5" thickBot="1">
+    <row r="81" spans="2:18" ht="65.25" thickBot="1">
       <c r="B81" s="79" t="s">
         <v>30</v>
       </c>
       <c r="C81" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D81" s="177" t="s">
         <v>240</v>
       </c>
       <c r="E81" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F81" s="177" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G81" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H81" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I81" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J81" s="177" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K81" s="28" t="s">
         <v>215</v>
       </c>
       <c r="L81" s="30" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M81" s="206"/>
       <c r="N81" s="36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O81" s="82"/>
       <c r="P81" s="228" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Q81" s="82"/>
       <c r="R81" s="151"/>
     </row>
-    <row r="82" spans="2:18" ht="13.5" thickTop="1">
+    <row r="82" spans="2:18" ht="13.6" thickTop="1">
       <c r="B82" s="80" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C82" s="178" t="s">
         <v>174</v>
@@ -76643,7 +77524,7 @@
         <v>32</v>
       </c>
       <c r="L82" s="41" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M82" s="153"/>
       <c r="N82" s="42" t="s">
@@ -76658,7 +77539,7 @@
     </row>
     <row r="83" spans="2:18">
       <c r="B83" s="23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C83" s="179" t="s">
         <v>174</v>
@@ -76688,7 +77569,7 @@
         <v>32</v>
       </c>
       <c r="L83" s="38" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M83" s="153"/>
       <c r="N83" s="44" t="s">
@@ -76696,14 +77577,14 @@
       </c>
       <c r="O83" s="48"/>
       <c r="P83" s="67" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="Q83" s="48"/>
       <c r="R83" s="153"/>
     </row>
     <row r="84" spans="2:18">
       <c r="B84" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C84" s="179" t="s">
         <v>174</v>
@@ -76733,7 +77614,7 @@
         <v>34</v>
       </c>
       <c r="L84" s="38" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M84" s="153"/>
       <c r="N84" s="44" t="s">
@@ -76748,7 +77629,7 @@
     </row>
     <row r="85" spans="2:18">
       <c r="B85" s="23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C85" s="179" t="s">
         <v>174</v>
@@ -76778,7 +77659,7 @@
         <v>35</v>
       </c>
       <c r="L85" s="38" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M85" s="149"/>
       <c r="N85" s="44" t="s">
@@ -76786,14 +77667,14 @@
       </c>
       <c r="O85" s="48"/>
       <c r="P85" s="67" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="Q85" s="48"/>
       <c r="R85" s="153"/>
     </row>
     <row r="86" spans="2:18">
       <c r="B86" s="23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C86" s="179" t="s">
         <v>174</v>
@@ -76823,7 +77704,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="38" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M86" s="149"/>
       <c r="N86" s="44" t="s">
@@ -76831,14 +77712,14 @@
       </c>
       <c r="O86" s="48"/>
       <c r="P86" s="67" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="Q86" s="48"/>
       <c r="R86" s="153"/>
     </row>
-    <row r="87" spans="2:18" ht="13.5" thickBot="1">
+    <row r="87" spans="2:18" ht="13.6" thickBot="1">
       <c r="B87" s="218" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C87" s="219" t="s">
         <v>174</v>
@@ -76865,10 +77746,10 @@
         <v>174</v>
       </c>
       <c r="K87" s="221" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L87" s="222" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M87" s="232"/>
       <c r="N87" s="223" t="s">
@@ -76892,28 +77773,31 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 C75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 C75" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"Index,Matrix Search"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="91" t="s">
         <v>91</v>
       </c>
@@ -76923,7 +77807,7 @@
       </c>
       <c r="D2" s="92"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="85" t="s">
         <v>89</v>
       </c>
@@ -76934,7 +77818,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -76945,7 +77829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -76956,7 +77840,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -76967,7 +77851,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -76978,7 +77862,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -76989,7 +77873,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -77000,7 +77884,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -77011,7 +77895,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -77022,7 +77906,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -77033,7 +77917,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -77044,7 +77928,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -77055,7 +77939,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -77077,7 +77961,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -77088,7 +77972,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -77099,7 +77983,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -77110,7 +77994,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -77157,7 +78041,7 @@
       <c r="C26" s="95"/>
       <c r="D26" s="81"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="96"/>
       <c r="D27" s="6"/>
@@ -77166,5 +78050,8 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>